--- a/InputFiles/GC/TC01_GC_phs002366_SmpTumSta-NSD_SmpType-Blood_LibStr_WXS.xlsx
+++ b/InputFiles/GC/TC01_GC_phs002366_SmpTumSta-NSD_SmpType-Blood_LibStr_WXS.xlsx
@@ -537,6 +537,7 @@
         <is>
           <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
 MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p)
+MATCH (f)-[:from_sample]-&gt;(samp)
 WHERE s.phs_accession = "phs002366"
   AND samp.sample_tumor_status = "Not specified in data"
   AND samp.sample_type = "Blood"
